--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Bandi di concorso.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Bandi di concorso.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="116">
   <si>
     <r>
       <t xml:space="preserve">
@@ -460,7 +460,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 Per consultare i criteri di assegnazione e fare domanda, [visita questo sito](URL).
 </t>
     </r>
@@ -471,7 +471,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -534,7 +534,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -816,7 +816,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">La tua prova pre-selettiva per il bando </t>
+      <t xml:space="preserve">In data </t>
     </r>
     <r>
       <rPr>
@@ -825,7 +825,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>&lt;oggetto del bando&gt;</t>
+      <t>&lt;gg/mm/aaaa&gt;</t>
     </r>
     <r>
       <rPr>
@@ -833,25 +833,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> ha avuto esito </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;esito&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">.
-In data ...  stato pubblicato l'esito della tua prova pre-selettiva per il bando </t>
+      <t xml:space="preserve"> è stato pubblicato l'esito della tua prova pre-selettiva per il bando </t>
     </r>
     <r>
       <rPr>
@@ -1103,7 +1085,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">  </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -1294,7 +1276,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
@@ -1314,13 +1296,16 @@
     </r>
   </si>
   <si>
+    <t>Fai domanda</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Vedi graduatoria</t>
+    <t>Vai alla graduatoria</t>
   </si>
   <si>
-    <t>Vedi Avviso</t>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
     <r>
@@ -1340,7 +1325,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1426,13 +1411,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'appuntamento tramite notifica push.</t>
   </si>
 </sst>
 </file>
@@ -2172,30 +2150,30 @@
         <v>92</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="I6" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="I6" s="34" t="s">
-        <v>92</v>
-      </c>
       <c r="J6" s="34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>59</v>
@@ -2227,121 +2205,121 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J9" s="34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J10" s="34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>59</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>59</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="H11" s="34" t="s">
         <v>59</v>
